--- a/NBFC-MF/Borrowers/Y_Seema_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Y_Seema_Weekly.xlsx
@@ -1138,77 +1138,81 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="19"/>
-      <c r="B13" s="23" t="str">
+      <c r="A13" s="19">
+        <v>46283</v>
+      </c>
+      <c r="B13" s="23">
         <f t="shared" si="3"/>
-        <v/>
+        <v>12</v>
       </c>
       <c r="C13" s="20"/>
-      <c r="D13" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E13" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F13" s="21" t="str">
+      <c r="D13" s="21">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="E13" s="21">
+        <f t="shared" si="1"/>
+        <v>157.21705653788118</v>
+      </c>
+      <c r="F13" s="21">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G13" s="21" t="str">
+        <v>1242.7829434621187</v>
+      </c>
+      <c r="G13" s="21">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H13" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>6597.85590128073</v>
+      </c>
+      <c r="H13" s="21">
+        <f t="shared" si="2"/>
+        <v>13402.144098719269</v>
       </c>
       <c r="J13" s="24" t="s">
         <v>21</v>
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>8400</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
-      <c r="B14" s="22" t="str">
+      <c r="A14" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B14" s="22">
         <f t="shared" si="3"/>
-        <v/>
+        <v>13</v>
       </c>
       <c r="C14" s="3"/>
-      <c r="D14" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E14" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F14" s="1" t="str">
+      <c r="D14" s="1">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="E14" s="1">
+        <f t="shared" si="1"/>
+        <v>132.29731719577319</v>
+      </c>
+      <c r="F14" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G14" s="1" t="str">
+        <v>1267.7026828042267</v>
+      </c>
+      <c r="G14" s="1">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H14" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>5330.1532184765038</v>
+      </c>
+      <c r="H14" s="1">
+        <f t="shared" si="2"/>
+        <v>14669.846781523496</v>
       </c>
       <c r="J14" s="10" t="s">
         <v>22</v>
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>7840.638844742849</v>
+        <v>5330.1532184765038</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1243,7 +1247,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>12159.361155257151</v>
+        <v>14669.846781523496</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Y_Seema_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Y_Seema_Weekly.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="193" sheetId="5" r:id="rId1"/>
+    <sheet name="231" sheetId="6" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="26">
   <si>
     <t>Date</t>
   </si>
@@ -91,6 +92,12 @@
   </si>
   <si>
     <t>Y_Seema</t>
+  </si>
+  <si>
+    <t>Payment Day</t>
+  </si>
+  <si>
+    <t>Saturday</t>
   </si>
 </sst>
 </file>
@@ -1138,7 +1145,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1175,7 +1182,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>5600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1212,70 +1219,74 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>5330.1532184765038</v>
+        <v>9.1336005425546318E-10</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="19"/>
-      <c r="B15" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A15" s="19">
+        <v>46295</v>
+      </c>
+      <c r="B15" s="23">
+        <f t="shared" si="3"/>
+        <v>14</v>
       </c>
       <c r="C15" s="20"/>
-      <c r="D15" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E15" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F15" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G15" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H15" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D15" s="21">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="E15" s="21">
+        <f t="shared" si="1"/>
+        <v>106.87789815324335</v>
+      </c>
+      <c r="F15" s="21">
+        <f t="shared" si="4"/>
+        <v>1293.1221018467566</v>
+      </c>
+      <c r="G15" s="21">
+        <f t="shared" si="5"/>
+        <v>4037.031116629747</v>
+      </c>
+      <c r="H15" s="21">
+        <f t="shared" si="2"/>
+        <v>15962.968883370253</v>
       </c>
       <c r="J15" s="12" t="s">
         <v>5</v>
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>14669.846781523496</v>
+        <v>19999.999999999087</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="2"/>
-      <c r="B16" s="22" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A16" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B16" s="22">
+        <f t="shared" si="3"/>
+        <v>15</v>
       </c>
       <c r="C16" s="3"/>
-      <c r="D16" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E16" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F16" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G16" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H16" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D16" s="1">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="E16" s="1">
+        <f t="shared" si="1"/>
+        <v>80.948780051758717</v>
+      </c>
+      <c r="F16" s="1">
+        <f t="shared" si="4"/>
+        <v>1319.0512199482414</v>
+      </c>
+      <c r="G16" s="1">
+        <f t="shared" si="5"/>
+        <v>2717.9798966815056</v>
+      </c>
+      <c r="H16" s="1">
+        <f t="shared" si="2"/>
+        <v>17282.020103318493</v>
       </c>
       <c r="J16" s="15" t="s">
         <v>18</v>
@@ -1286,31 +1297,33 @@
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="19"/>
-      <c r="B17" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A17" s="19">
+        <v>46300</v>
+      </c>
+      <c r="B17" s="23">
+        <f t="shared" si="3"/>
+        <v>16</v>
       </c>
       <c r="C17" s="20"/>
-      <c r="D17" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E17" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F17" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G17" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H17" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D17" s="21">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="E17" s="21">
+        <f t="shared" si="1"/>
+        <v>54.499742628996877</v>
+      </c>
+      <c r="F17" s="21">
+        <f t="shared" si="4"/>
+        <v>1345.500257371003</v>
+      </c>
+      <c r="G17" s="21">
+        <f t="shared" si="5"/>
+        <v>1372.4796393105025</v>
+      </c>
+      <c r="H17" s="21">
+        <f t="shared" si="2"/>
+        <v>18627.520360689497</v>
       </c>
       <c r="J17" s="17" t="s">
         <v>19</v>
@@ -1321,31 +1334,33 @@
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="22" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A18" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B18" s="22">
+        <f t="shared" si="3"/>
+        <v>17</v>
       </c>
       <c r="C18" s="3"/>
-      <c r="D18" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E18" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F18" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G18" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H18" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D18" s="1">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="E18" s="1">
+        <f t="shared" si="1"/>
+        <v>27.520360690410925</v>
+      </c>
+      <c r="F18" s="1">
+        <f t="shared" si="4"/>
+        <v>1372.4796393095892</v>
+      </c>
+      <c r="G18" s="1">
+        <f t="shared" si="5"/>
+        <v>9.1336005425546318E-10</v>
+      </c>
+      <c r="H18" s="1">
+        <f t="shared" si="2"/>
+        <v>19999.999999999087</v>
       </c>
     </row>
   </sheetData>
@@ -1353,4 +1368,634 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K18"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.85546875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="8.5703125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" style="5" customWidth="1"/>
+    <col min="4" max="7" width="14.7109375" style="5" customWidth="1"/>
+    <col min="8" max="8" width="13" style="5" customWidth="1"/>
+    <col min="9" max="9" width="1.28515625" style="5" customWidth="1"/>
+    <col min="10" max="10" width="23.5703125" style="5" customWidth="1"/>
+    <col min="11" max="11" width="23.140625" style="5" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="33" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="7"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B2" s="22">
+        <f>IF(A2&lt;&gt;"",1,"")</f>
+        <v>1</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="1">
+        <f t="shared" ref="D2:D18" si="0">IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),$K$9,"")</f>
+        <v>2100</v>
+      </c>
+      <c r="E2" s="1">
+        <f>IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),$K$7*$K$8,"")</f>
+        <v>601.54686238338741</v>
+      </c>
+      <c r="F2" s="1">
+        <f>IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),D2-E2,"")</f>
+        <v>1498.4531376166126</v>
+      </c>
+      <c r="G2" s="1">
+        <f>IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),$K$7-F2,"")</f>
+        <v>28501.546862383388</v>
+      </c>
+      <c r="H2" s="1">
+        <f>IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),$K$7-G2,"")</f>
+        <v>1498.4531376166124</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="25" t="str">
+        <f ca="1">IF(K3&lt;&gt;"",
+   "L" &amp; TEXT(K7,"0") &amp;
+   IF(J10="Weeks","W","D") &amp; K10 &amp;
+   "-" &amp; K3 &amp;
+   "-N" &amp; RIGHT(CELL("filename",A1),LEN(CELL("filename",A1))-FIND("]",CELL("filename",A1))),
+   "")</f>
+        <v>L30000W17-Y_Seema-N231</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="19"/>
+      <c r="B3" s="23" t="str">
+        <f>IF(A3&lt;&gt;"",B2+1,"")</f>
+        <v/>
+      </c>
+      <c r="C3" s="20"/>
+      <c r="D3" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E3" s="21" t="str">
+        <f t="shared" ref="E3:E18" si="1">IF(AND($A3&lt;&gt;"",$B3&lt;&gt;""),G2*$K$8,"")</f>
+        <v/>
+      </c>
+      <c r="F3" s="21" t="str">
+        <f>IF(AND($A3&lt;&gt;"",$B3&lt;&gt;""),D3-E3,"")</f>
+        <v/>
+      </c>
+      <c r="G3" s="21" t="str">
+        <f>IF(AND($A3&lt;&gt;"",$B3&lt;&gt;""),G2-F3,"")</f>
+        <v/>
+      </c>
+      <c r="H3" s="21" t="str">
+        <f t="shared" ref="H3:H18" si="2">IF(AND($A3&lt;&gt;"",$B3&lt;&gt;""),$K$7-G3,"")</f>
+        <v/>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K3" s="26" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="2"/>
+      <c r="B4" s="22" t="str">
+        <f t="shared" ref="B4:B18" si="3">IF(A4&lt;&gt;"",B3+1,"")</f>
+        <v/>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E4" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F4" s="1" t="str">
+        <f t="shared" ref="F4:F18" si="4">IF(AND($A4&lt;&gt;"",$B4&lt;&gt;""),D4-E4,"")</f>
+        <v/>
+      </c>
+      <c r="G4" s="1" t="str">
+        <f t="shared" ref="G4:G18" si="5">IF(AND($A4&lt;&gt;"",$B4&lt;&gt;""),G3-F4,"")</f>
+        <v/>
+      </c>
+      <c r="H4" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" s="26"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="19"/>
+      <c r="B5" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C5" s="20"/>
+      <c r="D5" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E5" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F5" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="G5" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H5" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K5" s="26"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="2"/>
+      <c r="B6" s="22" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E6" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F6" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="G6" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H6" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K6" s="26"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="19"/>
+      <c r="B7" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C7" s="20"/>
+      <c r="D7" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E7" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F7" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="G7" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H7" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K7" s="27">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="2"/>
+      <c r="B8" s="22" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E8" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F8" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="G8" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H8" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K8" s="6">
+        <f>RATE(K10,-K9,K7)</f>
+        <v>2.0051562079446247E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="19"/>
+      <c r="B9" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C9" s="20"/>
+      <c r="D9" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E9" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F9" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="G9" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H9" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K9" s="28">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="2"/>
+      <c r="B10" s="22" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E10" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F10" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="G10" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H10" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="K10" s="29">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="19"/>
+      <c r="B11" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C11" s="20"/>
+      <c r="D11" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E11" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F11" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="G11" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H11" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J11" s="14"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="2"/>
+      <c r="B12" s="22" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C12" s="3"/>
+      <c r="D12" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E12" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F12" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="G12" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H12" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K12" s="9">
+        <f>IFERROR(MAX($B:$B),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="19"/>
+      <c r="B13" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C13" s="20"/>
+      <c r="D13" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E13" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F13" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="G13" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H13" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J13" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="K13" s="11">
+        <f>(K10*K9)-K9*K12</f>
+        <v>33600</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="2"/>
+      <c r="B14" s="22" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C14" s="3"/>
+      <c r="D14" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E14" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F14" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="G14" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H14" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J14" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="K14" s="11">
+        <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
+        <v>28501.546862383388</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="19"/>
+      <c r="B15" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C15" s="20"/>
+      <c r="D15" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E15" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F15" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="G15" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H15" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J15" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="K15" s="13">
+        <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
+        <v>1498.4531376166124</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="2"/>
+      <c r="B16" s="22" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C16" s="3"/>
+      <c r="D16" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E16" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F16" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="G16" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H16" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J16" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="19"/>
+      <c r="B17" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C17" s="20"/>
+      <c r="D17" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E17" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F17" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="G17" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H17" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J17" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="K17" s="16"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" s="2"/>
+      <c r="B18" s="22" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C18" s="3"/>
+      <c r="D18" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E18" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F18" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="G18" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H18" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J18" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="K18" s="18">
+        <f xml:space="preserve"> IF(A2,(K17 + (17*7)),"")</f>
+        <v>119</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>